--- a/docs/downloads/04/tbl_schooling_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_schooling_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">

--- a/docs/downloads/04/tbl_schooling_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_schooling_marovoay_tous.xlsx
@@ -391,7 +391,7 @@
         <v>51</v>
       </c>
       <c r="D2">
-        <v>26.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -409,7 +409,7 @@
         <v>140</v>
       </c>
       <c r="D3">
-        <v>73.3</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
@@ -427,7 +427,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -445,7 +445,7 @@
         <v>137</v>
       </c>
       <c r="D5">
-        <v>93.2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>12.3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         <v>143</v>
       </c>
       <c r="D9">
-        <v>87.7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -535,7 +535,7 @@
         <v>111</v>
       </c>
       <c r="D10">
-        <v>18.3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -553,7 +553,7 @@
         <v>497</v>
       </c>
       <c r="D11">
-        <v>81.7</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
